--- a/Data/Excel/world_resource.xlsx
+++ b/Data/Excel/world_resource.xlsx
@@ -374,7 +374,7 @@
     </row>
     <row r="5">
       <c r="B5">
-        <v>1001</v>
+        <v>30300001</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -388,7 +388,7 @@
         <v>2</v>
       </c>
       <c r="F5">
-        <v>1001</v>
+        <v>30400001</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -413,7 +413,7 @@
     </row>
     <row r="6">
       <c r="B6">
-        <v>1002</v>
+        <v>30300002</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -427,7 +427,7 @@
         <v>2</v>
       </c>
       <c r="F6">
-        <v>1002</v>
+        <v>30400002</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -452,7 +452,7 @@
     </row>
     <row r="7">
       <c r="B7">
-        <v>1003</v>
+        <v>30300003</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -472,7 +472,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>2022</v>
+        <v>30002002</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -491,7 +491,7 @@
     </row>
     <row r="8">
       <c r="B8">
-        <v>1004</v>
+        <v>30300004</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -511,7 +511,7 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>2023</v>
+        <v>30002003</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -530,7 +530,7 @@
     </row>
     <row r="9">
       <c r="B9">
-        <v>1005</v>
+        <v>30300005</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -544,7 +544,7 @@
         <v>2</v>
       </c>
       <c r="F9">
-        <v>1005</v>
+        <v>30400005</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -569,7 +569,7 @@
     </row>
     <row r="10">
       <c r="B10">
-        <v>1006</v>
+        <v>30300006</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -583,7 +583,7 @@
         <v>2</v>
       </c>
       <c r="F10">
-        <v>1006</v>
+        <v>30400006</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -608,7 +608,7 @@
     </row>
     <row r="11">
       <c r="B11">
-        <v>1007</v>
+        <v>30300007</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -622,7 +622,7 @@
         <v>2</v>
       </c>
       <c r="F11">
-        <v>1007</v>
+        <v>30400007</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -647,7 +647,7 @@
     </row>
     <row r="12">
       <c r="B12">
-        <v>1008</v>
+        <v>30300008</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -664,7 +664,7 @@
         <v>0</v>
       </c>
       <c r="G12">
-        <v>2201</v>
+        <v>30902015</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -686,7 +686,7 @@
     </row>
     <row r="13">
       <c r="B13">
-        <v>1009</v>
+        <v>30300009</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         <v>0</v>
       </c>
       <c r="G13">
-        <v>2202</v>
+        <v>30902016</v>
       </c>
       <c r="H13">
         <v>0</v>
@@ -725,7 +725,7 @@
     </row>
     <row r="14">
       <c r="B14">
-        <v>1010</v>
+        <v>30300010</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
         <v>0</v>
       </c>
       <c r="H14">
-        <v>2021</v>
+        <v>30002001</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
